--- a/workspace/powerbi_export/AFW_PowerBI_Data.xlsx
+++ b/workspace/powerbi_export/AFW_PowerBI_Data.xlsx
@@ -25061,7 +25061,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-05T04:29:52.889025+00:00</t>
+          <t>2026-06-05T04:46:19.936410+00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
